--- a/src/main/java/pageobjectdemo/demowebshop.xlsx
+++ b/src/main/java/pageobjectdemo/demowebshop.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianselvarajaugustine/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianselvarajaugustine/eclipse-workspace/JavaTest/src/main/java/pageobjectdemo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69810319-6DA6-EF42-A560-4552A1B3C091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92762F7E-80A9-F54B-AEBF-25700C1AFB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{0D6EBABB-6485-3B43-98F2-6B4FE1200008}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" activeTab="1" xr2:uid="{0D6EBABB-6485-3B43-98F2-6B4FE1200008}"/>
   </bookViews>
   <sheets>
     <sheet name="userInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="registeredUsers" sheetId="2" r:id="rId2"/>
+    <sheet name="orders" sheetId="3" r:id="rId2"/>
+    <sheet name="registeredUsers" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
   <si>
     <t>FirstName</t>
   </si>
@@ -156,6 +157,15 @@
   </si>
   <si>
     <t>Password130</t>
+  </si>
+  <si>
+    <t>CustomerID</t>
+  </si>
+  <si>
+    <t>Ordernum</t>
+  </si>
+  <si>
+    <t>DROP &gt; Truncate &gt; Delete</t>
   </si>
 </sst>
 </file>
@@ -532,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC86E765-7E95-0A4D-9D39-0B0C4D69E2BF}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -542,7 +552,7 @@
     <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -561,8 +571,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -581,8 +594,11 @@
       <c r="F2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>78823</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -601,8 +617,11 @@
       <c r="F3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>78923</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -621,8 +640,11 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <v>79023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -641,8 +663,11 @@
       <c r="F5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <v>79123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -661,8 +686,11 @@
       <c r="F6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>79223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -681,8 +709,11 @@
       <c r="F7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>79323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -701,8 +732,11 @@
       <c r="F8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>79423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -720,6 +754,9 @@
       </c>
       <c r="F9" t="s">
         <v>39</v>
+      </c>
+      <c r="G9">
+        <v>79523</v>
       </c>
     </row>
   </sheetData>
@@ -732,9 +769,361 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2E6551-B63D-3E4E-8F47-8C442813C06D}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>202507001</v>
+      </c>
+      <c r="B2">
+        <v>78823</v>
+      </c>
+      <c r="E2" t="str">
+        <f>_xlfn.CONCAT("(",A2,",",B2,")",",")</f>
+        <v>(202507001,78823),</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>202507002</v>
+      </c>
+      <c r="B3">
+        <v>78824</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E28" si="0">_xlfn.CONCAT("(",A3,",",B3,")",",")</f>
+        <v>(202507002,78824),</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>202507003</v>
+      </c>
+      <c r="B4">
+        <v>78825</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507003,78825),</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>202507004</v>
+      </c>
+      <c r="B5">
+        <v>78826</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507004,78826),</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>202507005</v>
+      </c>
+      <c r="B6">
+        <v>78827</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507005,78827),</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>202507006</v>
+      </c>
+      <c r="B7">
+        <v>78828</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507006,78828),</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>202507007</v>
+      </c>
+      <c r="B8">
+        <v>78829</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507007,78829),</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>202507008</v>
+      </c>
+      <c r="B9">
+        <v>78830</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507008,78830),</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>202507009</v>
+      </c>
+      <c r="B10">
+        <v>78831</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507009,78831),</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>202507010</v>
+      </c>
+      <c r="B11">
+        <v>78823</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507010,78823),</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>202507011</v>
+      </c>
+      <c r="B12">
+        <v>78824</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507011,78824),</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>202507012</v>
+      </c>
+      <c r="B13">
+        <v>78825</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507012,78825),</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>202507013</v>
+      </c>
+      <c r="B14">
+        <v>78826</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507013,78826),</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>202507014</v>
+      </c>
+      <c r="B15">
+        <v>78827</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507014,78827),</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>202507015</v>
+      </c>
+      <c r="B16">
+        <v>78828</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507015,78828),</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>202507016</v>
+      </c>
+      <c r="B17">
+        <v>78829</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507016,78829),</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>202507017</v>
+      </c>
+      <c r="B18">
+        <v>78830</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507017,78830),</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>202507018</v>
+      </c>
+      <c r="B19">
+        <v>78831</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507018,78831),</v>
+      </c>
+      <c r="I19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>202507019</v>
+      </c>
+      <c r="B20">
+        <v>78823</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507019,78823),</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>202507020</v>
+      </c>
+      <c r="B21">
+        <v>78824</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507020,78824),</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>202507021</v>
+      </c>
+      <c r="B22">
+        <v>78825</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507021,78825),</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>202507022</v>
+      </c>
+      <c r="B23">
+        <v>78826</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507022,78826),</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>202507023</v>
+      </c>
+      <c r="B24">
+        <v>78827</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507023,78827),</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>202507024</v>
+      </c>
+      <c r="B25">
+        <v>78828</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507024,78828),</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>202507025</v>
+      </c>
+      <c r="B26">
+        <v>78829</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507025,78829),</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>202507026</v>
+      </c>
+      <c r="B27">
+        <v>78830</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507026,78830),</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>202507027</v>
+      </c>
+      <c r="B28">
+        <v>78831</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>(202507027,78831),</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5330C87E-6C6E-2140-85C2-FA80B4BBC4C0}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -744,6 +1133,30 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/java/pageobjectdemo/demowebshop.xlsx
+++ b/src/main/java/pageobjectdemo/demowebshop.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianselvarajaugustine/eclipse-workspace/JavaTest/src/main/java/pageobjectdemo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92762F7E-80A9-F54B-AEBF-25700C1AFB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9078FB-639F-194C-8EB2-1C8E53F22FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" activeTab="1" xr2:uid="{0D6EBABB-6485-3B43-98F2-6B4FE1200008}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" xr2:uid="{0D6EBABB-6485-3B43-98F2-6B4FE1200008}"/>
   </bookViews>
   <sheets>
     <sheet name="userInfo" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
   <si>
     <t>FirstName</t>
   </si>
@@ -114,27 +114,12 @@
     <t>FirstName789.LastName789@test23.com</t>
   </si>
   <si>
-    <t>FirstName790.LastName790@test23.com</t>
-  </si>
-  <si>
     <t>FirstName791.LastName791@test23.com</t>
   </si>
   <si>
-    <t>FirstName792.LastName792@test23.com</t>
-  </si>
-  <si>
     <t>FirstName793.LastName793@test23.com</t>
   </si>
   <si>
-    <t>FirstName794.LastName794@test23.com</t>
-  </si>
-  <si>
-    <t>FirstName795.LastName795@test23.com</t>
-  </si>
-  <si>
-    <t>FirstName788.LastName788@test23.com</t>
-  </si>
-  <si>
     <t>Password123</t>
   </si>
   <si>
@@ -166,12 +151,49 @@
   </si>
   <si>
     <t>DROP &gt; Truncate &gt; Delete</t>
+  </si>
+  <si>
+    <t>Sachin.R2@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7881.LastName788@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7892.LastName789@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7903.LastName790@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7911.LastName791@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7921.LastName792@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7931.LastName793@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7941.LastName794@test23.com</t>
+  </si>
+  <si>
+    <t>FirstName7951.LastName795@test23.com</t>
+  </si>
+  <si>
+    <t>Sara.A001@test23.com</t>
+  </si>
+  <si>
+    <t>Rahul.D3@test23.com</t>
+  </si>
+  <si>
+    <t>Yuvi.A004@test23.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -542,227 +564,207 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC86E765-7E95-0A4D-9D39-0B0C4D69E2BF}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.83203125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.5"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="36.33203125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F6" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F7" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="G2">
-        <v>78823</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3">
-        <v>78923</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B9" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F9" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="G4">
-        <v>79023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>79123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6">
-        <v>79223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>79323</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>79423</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9">
-        <v>79523</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{DE78F87F-6D11-B54B-A720-650221DDE4E2}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{C28C414B-50A1-6B4D-AFF3-F0A7B075A8A8}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{F9917897-4E7D-994D-8570-D910A936B13A}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{389E218A-9B9F-6C46-8F7B-EAA1E1F80115}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{E7DA4797-8516-8A4C-8766-9C970D574F87}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{2461F223-D8A1-1F4B-82F0-D6CF36F4BCA0}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{53774AF8-92E0-0242-9F8B-27555661D7A1}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{51C022D6-5088-9049-9EAC-015E80B36441}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -773,340 +775,340 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.1640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" t="s">
-        <v>40</v>
+      <c r="A1" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>202507001</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>78823</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2" t="str" s="0">
         <f>_xlfn.CONCAT("(",A2,",",B2,")",",")</f>
         <v>(202507001,78823),</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>202507002</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>78824</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3" t="str" s="0">
         <f t="shared" ref="E3:E28" si="0">_xlfn.CONCAT("(",A3,",",B3,")",",")</f>
         <v>(202507002,78824),</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>202507003</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>78825</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507003,78825),</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="0">
         <v>202507004</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>78826</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507004,78826),</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>202507005</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>78827</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507005,78827),</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>202507006</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>78828</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E7" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507006,78828),</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>202507007</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>78829</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E8" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507007,78829),</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>202507008</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>78830</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507008,78830),</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>202507009</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>78831</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507009,78831),</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="0">
         <v>202507010</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>78823</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507010,78823),</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="A12" s="0">
         <v>202507011</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="0">
         <v>78824</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E12" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507011,78824),</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="A13" s="0">
         <v>202507012</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0">
         <v>78825</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E13" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507012,78825),</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="A14" s="0">
         <v>202507013</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="0">
         <v>78826</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E14" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507013,78826),</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="A15" s="0">
         <v>202507014</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="0">
         <v>78827</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E15" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507014,78827),</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="A16" s="0">
         <v>202507015</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="0">
         <v>78828</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E16" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507015,78828),</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="A17" s="0">
         <v>202507016</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="0">
         <v>78829</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E17" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507016,78829),</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18">
+      <c r="A18" s="0">
         <v>202507017</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="0">
         <v>78830</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E18" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507017,78830),</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="A19" s="0">
         <v>202507018</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="0">
         <v>78831</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E19" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507018,78831),</v>
       </c>
-      <c r="I19" t="s">
-        <v>42</v>
+      <c r="I19" t="s" s="0">
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="A20" s="0">
         <v>202507019</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="0">
         <v>78823</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E20" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507019,78823),</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="A21" s="0">
         <v>202507020</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="0">
         <v>78824</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E21" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507020,78824),</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="A22" s="0">
         <v>202507021</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="0">
         <v>78825</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E22" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507021,78825),</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="A23" s="0">
         <v>202507022</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="0">
         <v>78826</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E23" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507022,78826),</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="A24" s="0">
         <v>202507023</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="0">
         <v>78827</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E24" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507023,78827),</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="A25" s="0">
         <v>202507024</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="0">
         <v>78828</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E25" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507024,78828),</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="A26" s="0">
         <v>202507025</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="0">
         <v>78829</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E26" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507025,78829),</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="A27" s="0">
         <v>202507026</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="0">
         <v>78830</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E27" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507026,78830),</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="A28" s="0">
         <v>202507027</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="0">
         <v>78831</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E28" t="str" s="0">
         <f t="shared" si="0"/>
         <v>(202507027,78831),</v>
       </c>
@@ -1118,18 +1120,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5330C87E-6C6E-2140-85C2-FA80B4BBC4C0}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="36.33203125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>4</v>
       </c>
     </row>
@@ -1137,24 +1139,64 @@
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="B2" t="s" s="0">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
